--- a/coretp/plans/zihintpause/Zihintpause_TP.xlsx
+++ b/coretp/plans/zihintpause/Zihintpause_TP.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/njoaquin/Documents/Clean Test Plans/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9F3ED77-D6CD-1E42-BEE7-B8B4B37514FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC3DAE88-7C6E-114A-83A3-6C2ED500D3DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="34560" windowHeight="21600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -99,15 +99,6 @@
     <t>Pause around spl instructions</t>
   </si>
   <si>
-    <t>Instruction = pick_any : {
-Vector cracked ops,
-CSR serilisation,
-Fence,
-Random instructions
-}
-Use the instruction before the Pause instruction</t>
-  </si>
-  <si>
     <t>SID_ZHP_05</t>
   </si>
   <si>
@@ -168,6 +159,14 @@
 System(instruction="pause")
 System(instruction="wfi")
 Comment(comment="WFI executed after Pause")</t>
+  </si>
+  <si>
+    <t>Instruction = pick_any : {
+CSR serilisation,
+Fence,
+Random instructions
+}
+Use the instruction before the Pause instruction</t>
   </si>
 </sst>
 </file>
@@ -732,7 +731,7 @@
         <v>9</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -762,7 +761,7 @@
         <v>16</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="388" x14ac:dyDescent="0.2">
@@ -773,25 +772,25 @@
         <v>18</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="187" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" t="s">
         <v>20</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="E7" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -803,6 +802,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100815CC0311B58BB469E58C0B9C6D5A1E3" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1488b9e29057bb05d7566911ae2a3b45">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e8037ae1-f799-41f0-b119-cbea2f4ab5d4" xmlns:ns3="b3c44bb9-2631-4400-93cf-11acafc6ee3a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="56dc4d26cafaf16f6501fc4cdb1e35ee" ns2:_="" ns3:_="">
     <xsd:import namespace="e8037ae1-f799-41f0-b119-cbea2f4ab5d4"/>
@@ -1051,15 +1059,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1072,6 +1071,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C567C887-C793-4505-943A-166E0B38CA38}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{37ACFF97-E671-417E-932E-F08BBE40CA40}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1090,14 +1097,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C567C887-C793-4505-943A-166E0B38CA38}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A8101412-6DB1-49E0-B835-B7D06440A03C}">
   <ds:schemaRefs>
